--- a/4p-index/STP_Lei-10-1999_Basic-Environmental-Law_4P-Index.xlsx
+++ b/4p-index/STP_Lei-10-1999_Basic-Environmental-Law_4P-Index.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>No explicit mention of 'plastics'; qualifies under plastics-relevance criterion (c) as a governance/EIA instrument that commonly applies to plastic-producing, packaging or waste-handling projects. Closely linked to the licensing instrument (Art. 46.º) below — EIA approval is an explicit precondition for licensing (mixed governance/regulatory nature; highest score (1, Regulatory) applied per Rule 10). Uncertain whether the (as-yet unpublished) list of activities requiring EIA (Art. 45.º(5)) would include plastics-manufacturing/packaging facilities; assumed yes.</t>
+          <t>Instrument type: Regulatory (1). No explicit mention of 'plastics'; qualifies under plastics-relevance criterion (c) as a governance/EIA instrument that commonly applies to plastic-producing, packaging or waste-handling projects. Closely linked to the licensing instrument (Art. 46.º) below — EIA approval is an explicit precondition for licensing (mixed governance/regulatory nature; highest score (1, Regulatory) applied per Rule 10). Uncertain whether the (as-yet unpublished) list of activities requiring EIA (Art. 45.º(5)) would include plastics-manufacturing/packaging facilities; assumed yes.</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Applies to any industrial, commercial or manufacturing establishment liable to pollute — including, by extension, plastics production, processing or packaging facilities and waste-handling sites (plastics-relevance criterion c). No plastics-specific language.</t>
+          <t>Instrument type: Regulatory (1). Applies to any industrial, commercial or manufacturing establishment liable to pollute — including, by extension, plastics production, processing or packaging facilities and waste-handling sites (plastics-relevance criterion c). No plastics-specific language.</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>No explicit mention of 'plastics', but directly governs waste and effluent handling generally, which in practice covers plastic waste streams (plastics-relevance criterion c: waste management obligations).</t>
+          <t>Instrument type: Regulatory (1). No explicit mention of 'plastics', but directly governs waste and effluent handling generally, which in practice covers plastic waste streams (plastics-relevance criterion c: waste management obligations).</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>Ban language ('resíduos... e outros' / 'waste... and other [waste]'; 'produtos que contenham substâncias... susceptíveis de... contribuam para a degradação do ambiente' / 'products containing substances... liable to... contribute to environmental degradation') is broad enough to cover dumping of plastic waste/debris (plastics-relevance criterion b/c), though plastics are not named. Enforcement is weak because actual sanctions require future special legislation (Art. 63.º).</t>
+          <t>Instrument type: Regulatory (1). Ban language ('resíduos... e outros' / 'waste... and other [waste]'; 'produtos que contenham substâncias... susceptíveis de... contribuam para a degradação do ambiente' / 'products containing substances... liable to... contribute to environmental degradation') is broad enough to cover dumping of plastic waste/debris (plastics-relevance criterion b/c), though plastics are not named. Enforcement is weak because actual sanctions require future special legislation (Art. 63.º).</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Broad enough to potentially cover import of hazardous plastic materials/products or plastic waste that cause environmental degradation (plastics-relevance criterion b/c), but plastics are not named. Coded lifecycle stage as 'Production' (upstream/import control point); could arguably be coded 'Consumption' instead — flagged as a borderline case.</t>
+          <t>Instrument type: Regulatory (1). Broad enough to potentially cover import of hazardous plastic materials/products or plastic waste that cause environmental degradation (plastics-relevance criterion b/c), but plastics are not named. Coded lifecycle stage as 'Production' (upstream/import control point); could arguably be coded 'Consumption' instead — flagged as a borderline case.</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.20 (Governance &amp; coordination)</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.475</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Multi-level, multi-sector coordination body: Art. 50.º composition spans Environment, Agriculture, Fisheries, Industry, Tourism, Health, Defence/Internal Order and Media ministries plus regional (Príncipe) and district (municipal) representatives — a valid coordination instrument under Rule 11. Coded lifecycle stage as 'Waste management' for schema-completion purposes only; the instrument is in fact cross-cutting/general governance rather than tied to one specific life-cycle stage. Relevant to plastics only insofar as CNA/CTNA oversee cross-sectoral environmental/waste policy generally (plastics-relevance criterion c); no plastics-specific mandate.</t>
+          <t>Instrument type: Governance &amp; coordination (0.2). Multi-level, multi-sector coordination body: Art. 50.º composition spans Environment, Agriculture, Fisheries, Industry, Tourism, Health, Defence/Internal Order and Media ministries plus regional (Príncipe) and district (municipal) representatives — a valid coordination instrument under Rule 11. Coded lifecycle stage as 'Waste management' for schema-completion purposes only; the instrument is in fact cross-cutting/general governance rather than tied to one specific life-cycle stage. Relevant to plastics only insofar as CNA/CTNA oversee cross-sectoral environmental/waste policy generally (plastics-relevance criterion c); no plastics-specific mandate.</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0.60 (Economic)</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Ring-fenced, dedicated fund with its own revenue sources (state budget allocations + natural-resource-use fees + compensations/indemnities) — drives policy-level Col M = 1. Not plastics-specific, but a general environmental fund that could in principle finance plastic-waste-related programmes (plastics-relevance criterion c). The separate management decree ('diploma próprio') referred to in Art. 53.º(1) has not been identified/located.</t>
+          <t>Instrument type: Economic (0.6). Ring-fenced, dedicated fund with its own revenue sources (state budget allocations + natural-resource-use fees + compensations/indemnities) — drives policy-level Col M = 1. Not plastics-specific, but a general environmental fund that could in principle finance plastic-waste-related programmes (plastics-relevance criterion c). The separate management decree ('diploma próprio') referred to in Art. 53.º(1) has not been identified/located.</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.60 (Economic)</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.425</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Enabling power only: the user-pays/polluter-pays fee on natural-resource use and effluent discharge is announced as a future instrument ('a definir') rather than an operative levy with a set rate — scored in_force = 0 per Rule 12, since no subordinate fee-setting decree operationalising it has been identified in this text. Would need to be cross-checked against later fee-setting regulations (e.g., the 1999 waste/EIA decrees referenced in the wider policy family) to confirm if since operationalised.</t>
+          <t>Instrument type: Economic (0.6). Enabling power only: the user-pays/polluter-pays fee on natural-resource use and effluent discharge is announced as a future instrument ('a definir') rather than an operative levy with a set rate — scored in_force = 0 per Rule 12, since no subordinate fee-setting decree operationalising it has been identified in this text. Would need to be cross-checked against later fee-setting regulations (e.g., the 1999 waste/EIA decrees referenced in the wider policy family) to confirm if since operationalised.</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1540,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>Mixed/borderline instrument: the no-fault civil liability rule in Art. 57.º ('Existe obrigação de indemnizar' / 'there is an obligation to indemnify') uses mandatory language and arguably could be scored in_force = 1 on its own (a reviewer could reasonably code this row as S = 1). However, the operative punitive/administrative sanctions regime for 'ecological offences' — including 'chemical pollution' (Art. 62.º(f)), which is the provision most readily linked to plastics-relevant harm — is explicitly deferred to future special legislation (Art. 63.º) and has therefore been scored as not yet in force (S = 0), consistent with Rule 12. No explicit mention of 'plastics'.</t>
+          <t>Instrument type: Regulatory (1). Mixed/borderline instrument: the no-fault civil liability rule in Art. 57.º ('Existe obrigação de indemnizar' / 'there is an obligation to indemnify') uses mandatory language and arguably could be scored in_force = 1 on its own (a reviewer could reasonably code this row as S = 1). However, the operative punitive/administrative sanctions regime for 'ecological offences' — including 'chemical pollution' (Art. 62.º(f)), which is the provision most readily linked to plastics-relevant harm — is explicitly deferred to future special legislation (Art. 63.º) and has therefore been scored as not yet in force (S = 0), consistent with Rule 12. No explicit mention of 'plastics'.</t>
         </is>
       </c>
     </row>

--- a/4p-index/STP_Lei-10-1999_Basic-Environmental-Law_4P-Index.xlsx
+++ b/4p-index/STP_Lei-10-1999_Basic-Environmental-Law_4P-Index.xlsx
@@ -588,61 +588,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -654,25 +640,19 @@
           <t>Art. 4.º(3): 'O estudo de impacte ambiental deve ser exigido como mecanismo de prevenção e minimização de qualquer impacto no ambiente.' / 'The environmental impact study must be required as a mechanism for preventing and minimising any impact on the environment.' Art. 45.º(1): plans, projects, works and actions liable to affect the environment 'devem... ser acompanhados de um estudo de impacte ambiental' / 'must... be accompanied by an environmental impact study'. Art. 45.º(6): 'A aprovação do estudo de impacto ambiental é condição essencial para o licenciamento das obras e trabalhos.' / 'Approval of the environmental impact study is an essential condition for licensing works and activities.'</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Art. 45.º(4): 'O Ministério competente em matéria de ambiente é responsável pela avaliação do estudo de impacte ambiental, emitindo, sobre ele, parecer obrigatório.' / 'The Ministry responsible for environmental matters is responsible for evaluating the environmental impact study, issuing a mandatory opinion on it.' (+0.25 responsible authority). Art. 45.º(3)(d): the EIA must include 'Resultado da consulta pública das populações afectadas' / 'Results of the public consultation of affected populations' (+0.25 monitoring/review mechanism). No fines/penalties for non-compliance are specified in this law (0 enforcement); the scope of activities requiring EIA is left to a future list to be published by the Ministry (Art. 45.º(5)), so not scored as unconditional.</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="V2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -701,61 +681,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -767,25 +733,19 @@
           <t>Art. 46.º(1): 'A construção, ampliação, instalação e funcionamento de estabelecimento e o exercício de actividades susceptíveis de poluir ou contaminar o ambiente dependem de prévio licenciamento pelo serviço competente do estado.' / 'The construction, expansion, installation and operation of establishments, and the pursuit of activities liable to pollute or contaminate the environment, are subject to prior licensing by the competent state service.' Art. 46.º(3): 'Os estabelecimentos que alterem as condições normais de salubridade e higiene do ambiente podem ser obrigados a transferir a sua actividade para local mais apropriado.' / 'Establishments that alter the normal conditions of environmental salubrity and hygiene may be required to relocate their activity to a more suitable location.'</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Art. 46.º(1): licensing by the 'serviço competente do estado' / 'competent state service' (+0.25 responsible authority, though not individually named). Art. 46.º(2): 'A autorização para o funcionamento exige o licenciamento prévio e a vistoria das obras ou instalações realizadas.' / 'Authorisation to operate requires prior licensing and inspection ('vistoria') of the works or installations carried out.' (+0.25 monitoring/inspection mechanism). No specific fines for operating without a licence are set out (0 enforcement). Relocation power is discretionary ('podem ser obrigados' / 'may be required'), so not scored as unconditional.</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="V3" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -814,61 +774,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -880,25 +826,19 @@
           <t>Art. 41.º(1): 'A emissão, transporte e destino final de resíduos e efluentes ficam condicionados a autorização prévia, devidamente titulada por uma guia de transporte da qual consta a sua origem e destino.' / 'The emission, transport and final destination of waste and effluents are subject to prior authorisation, duly evidenced by a transport permit stating their origin and destination.' Art. 41.º(2): 'Os resíduos ou efluentes devem ser recolhidos, armazenado, transportados, eliminados ou reutilizados de forma a que não constituam perigo imediato ou potencial para a saúde nem causem prejuízo ao ambiente.' / 'Waste or effluents must be collected, stored, transported, disposed of or reused in a manner that does not constitute an immediate or potential danger to health, nor cause harm to the environment.' Art. 41.º(3): 'A descarga de resíduos e efluentes só pode ser efectuada em locais determinados para o efeito pelas entidades competentes.' / 'The discharge of waste and effluents may only take place at locations designated for that purpose by the competent authorities.'</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>'entidades competentes' / 'competent authorities' designated to authorise waste/effluent handling and designate discharge sites (+0.25 responsible authority). The mandatory 'guia de transporte' (transport permit) recording origin and destination of waste (+0.25 monitoring/data-collection requirement). No specific fines are named in this article for breach (0 enforcement — general sanctions are deferred to special legislation under Art. 63.º). The obligation applies to all waste and effluents without stated exemptions (+0.25 unconditional).</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
+      <c r="V4" s="2" t="n">
+        <v>0.875</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
@@ -927,61 +867,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -993,25 +919,19 @@
           <t>Art. 60.º: 'Em território nacional ou em área sob jurisdição da República de São Tomé e Príncipe é proibido lançar, depositar, ou por qualquer outra forma introduzir nos componentes ambientais resíduos radioactivos e outros, bem como produtos que contenham substâncias ou microorganismos susceptíveis de alterar ou tornar impróprias para as suas aplicações ou componentes ambientais e contribuam para a degradação do ambiente.' / 'Within national territory or in an area under the jurisdiction of the Democratic Republic of São Tomé and Príncipe, it is prohibited to release, deposit, or otherwise introduce into environmental components radioactive and other waste, as well as products containing substances or micro-organisms liable to alter or render environmental components unfit for their uses, and which contribute to environmental degradation.'</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>No specific authority is named in this article for enforcing the ban (0). No monitoring mechanism specified in this article (0). No fines/penalties are set out here — Art. 63.º expressly defers 'A tipificação dos crimes e transgressões contra o ambiente e a determinação das sanções aplicáveis' / 'the classification of environmental crimes and offences, and the determination of applicable sanctions' to future 'legislação especial' / 'special legislation' (0 enforcement). The prohibition itself is stated as a blanket ban with no exemptions (+0.25 unconditional).</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0.625</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>0.625</v>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
@@ -1040,61 +960,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -1106,25 +1012,19 @@
           <t>Art. 61.º: 'É proibida a importação de quaisquer actividades, produtos ou matérias que causem grave degradação do ambiente ou que sejam potencialmente nocivas para a saúde humana e para os ecossistemas da República de São Tomé e Príncipe.' / 'The importation of any activities, products or materials that cause serious environmental degradation, or that are potentially harmful to human health and to the ecosystems of the Republic of São Tomé and Príncipe, is prohibited.'</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>No specific customs/enforcement authority is named in this article (0). No monitoring/inspection mechanism specified here (0). No fines are set out — general sanctions again deferred to future special legislation under Art. 63.º (0 enforcement). The ban is stated without exemptions (+0.25 unconditional).</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0.625</t>
-        </is>
+      <c r="V6" s="2" t="n">
+        <v>0.625</v>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
@@ -1153,61 +1053,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O7" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
@@ -1219,25 +1105,19 @@
           <t>Art. 47.º: 'Compete ao Governo, através do Ministério responsável, a definição e condução de uma política global no domínio do ambiente para o desenvolvimento sustentável...' / 'It is the Government's responsibility, through the responsible Ministry, to define and conduct an overall policy in the field of the environment for sustainable development...'. Art. 48.º(1): 'É criada a Comissão Nacional do Ambiente, adiante denominada CNA, organismo consultivo, dotado de autonomia administrativa e financeira...' / 'The National Environmental Commission, hereinafter referred to as the CNA, is hereby created, an advisory body endowed with administrative and financial autonomy...'. Art. 52.º(1): 'À Comissão Técnica Nacional do Ambiente compete assegurar a representação, o apoio e a colaboração de todos os sectores nela representados e coordenar as respectivas intervenções no âmbito da política nacional do ambiente...' / 'The National Technical Environmental Commission (CTNA) is responsible for ensuring the representation, support and collaboration of all sectors represented on it, and for coordinating their respective interventions within the scope of national environmental policy...'.</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>CNA and CTNA and the responsible Ministry are explicitly established/designated (+0.25 responsible authority). CNA's mandate includes to 'Acompanhar e pronunciar-se sobre os programas e actividades relacionados com o ambiente da responsabilidade dos vários departamentos do Estado' / 'Monitor and issue opinions on environment-related programmes and activities under the responsibility of the various State departments' (Art. 49.º(a)) (+0.25 monitoring). No enforcement powers are granted to these advisory/coordinating bodies (0 enforcement). No exemptions are stated regarding the institutional mandate (+0.25 unconditional).</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0.475</t>
-        </is>
+      <c r="V7" s="2" t="n">
+        <v>0.475</v>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
@@ -1266,61 +1146,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O8" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
@@ -1332,25 +1198,19 @@
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Art. 51.º(1)(c): the CNA President's duties include 'Gerir os fundos colocados à disposição do CNA' / 'Manage the funds made available to the CNA' (+0.25 responsible authority). No enforcement mechanism applicable to a fund (0). No explicit audit/reporting/monitoring requirement for the fund is stated in the text (0 monitoring). No exemptions are stated regarding the fund's creation or its revenue sources (+0.25 unconditional); the detailed management regime is left to a future separate decree ('diploma próprio'), which is an implementation detail rather than an exemption.</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V8" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
@@ -1379,61 +1239,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O9" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
@@ -1445,25 +1291,19 @@
           <t>Art. 12.º: 'Os utilizadores dos meios e recursos naturais devem pagar por essa utilização um preço justo, a definir pela entidade governamental responsável pelo ambiente independentemente de causarem ou não deterioração desses meios e recursos.' / 'Users of natural means and resources must pay a fair price for such use, to be defined by the government entity responsible for the environment, regardless of whether they cause deterioration of those means and resources or not.' Art. 43.º(t): among the listed policy instruments is 'A fixação de taxas a aplicar pela utilização de recursos naturais e componentes ambientais, bem como pela rejeição de efluentes.' / 'The setting of fees to be applied for the use of natural resources and environmental components, as well as for the discharge of effluents.'</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="S9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
           <t>The 'entidade governamental responsável pelo ambiente' / 'government entity responsible for the environment' is designated as the body that will set the fee (+0.25 responsible authority). No actual rate, collection mechanism, monitoring or enforcement/penalty for non-payment is specified in this law — the price is explicitly 'a definir' / 'to be defined' in the future (0 for the other three sub-scores).</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0.425</t>
-        </is>
+      <c r="V9" s="2" t="n">
+        <v>0.425</v>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
@@ -1492,61 +1332,47 @@
           <t>General cross-cutting framework law establishing São Tomé and Príncipe's environmental policy, founding principles and institutional system for sustainable development. It does not target plastics specifically and contains no explicit reference to 'plastics' or 'synthetic polymers'; instead it lays down cross-cutting principles (precaution and prevention, polluter-pays, user-pays, prior environmental impact assessment, adequate waste management) and general instruments (prior licensing, waste/effluent authorisation, an environmental fund, coordinating bodies) that later plastics-relevant instruments (e.g., the 1999 waste and EIA decrees and the 2020 plastic bag law referred to in the policy family) implement and operationalise.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Legislation enacted by the Assembleia Nacional (National Assembly) under Article 86(b) of the Constitution and promulgated by the President of the Republic — preamble: 'A Assembleia Nacional decreta, nos termos da alínea b) do Artigo 86º da constituição o seguinte' / 'The National Assembly decrees, under paragraph b) of Article 86 of the Constitution, the following'; closing: 'Promulgada em 15 de Abril de 1999' / 'Promulgated on 15 April 1999'. This is an Act of Parliament, not an executive or ministerial decree.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>agriculture, fisheries, industry, tourism, health, municipalities, water, waste management, chemicals, forestry, commerce, defence/public order, media</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Art. 53.º(1): 'É criado um Fundo para o Ambiente, cuja gestão é definida em diploma próprio.' / 'A Fund for the Environment is hereby created, the management of which shall be defined by a separate decree.' Art. 53.º(2): 'Integram designadamente o fundo para o ambiente dotações do Orçamento Geral do Estado, o produto das taxas a aplicar pela utilização dos recursos naturais bem como indemnizações e compensações.' / 'The environmental fund shall include, in particular, allocations from the General State Budget, revenue from fees applied to the use of natural resources, as well as indemnities and compensation.'</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
@@ -1558,25 +1384,19 @@
           <t>Art. 57.º: 'Existe obrigação de indemnizar, independentemente da culpa, sempre que o agente tenha causado danos designativos no ambiente, em virtude de uma acção especialmente perigosa, ainda que com respeito das normas aplicáveis.' / 'There is an obligation to indemnify, regardless of fault, whenever the agent has caused significant damage to the environment by virtue of a particularly dangerous action, even where applicable rules have been complied with.' Art. 62.º defines 'ofensa ecológica' / 'ecological offence', including (f) 'A poluição química: todo o acto ou facto que consista afectar a saúde ou o ambiente através de substâncias químicas, tóxicas ou radioactivas' / 'Chemical pollution: any act or fact consisting of affecting health or the environment through chemical, toxic or radioactive substances.' Art. 63.º: 'A tipificação dos crimes e transgressões contra o ambiente e a determinação das sanções aplicáveis consta de legislação especial.' / 'The classification of environmental crimes and offences, and the determination of applicable sanctions, shall be set out in special legislation.'</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="S10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t>No specific authority is named in these articles for imposing sanctions (0). No monitoring mechanism specified (0). No fines/penalties are set out — Art. 63.º expressly defers the classification of offences and the applicable sanctions to future special legislation (0 enforcement). Conditional on that future special legislation being adopted (0 unconditional).</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="V10" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
